--- a/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="121">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 7: Produktvalg med én knapp faktor (V5)</t>
   </si>
@@ -140,18 +140,48 @@
     <t xml:space="preserve">a)  Hvor mange montørtimer ville det tatt å ta alle forespørslene i april? Gang antallet med timer per oppdrag for hver type og legg sammen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flaskehals = den faktoren som først og fremst begrenser produksjons- eller salgsmengden (Økonomistyring 7.1). Behov for den knappe faktoren = antall × forbruk per enhet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Ranger etter dekningsbidrag per montørtime og fyll timene ovenfra og ned. Hvor mange boliginstallasjoner får plass i planen?</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet av den knappe faktoren = DB per enhet / forbruk av den knappe faktoren per enhet (Økonomistyring 7.2, tabell 7.3). Planen fyller kapasiteten i rangert rekkefølge, begrenset av hvor mye som kan selges (oppgave 4 c–e i kapitlet).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Samlet dekningsbidrag i aprilplanen, i kroner: antall av hver type ganger DB per oppdrag, lagt sammen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Samlet dekningsbidrag = summen av antall × DB per enhet for hver type (Økonomistyring 7.2; dekningsbidrag fra kap. 5.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Ronny sier: «Nybygg gir 2 100 kroner per jobb, over dobbelt så mye som en boliginstallasjon. Ta nybyggene før boligene.» Hva er riktig svar?   A: Ronny har rett: høyest dekningsbidrag per jobb skal først   B: Ronny tar feil: nybygg gir 233 kr per montørtime og bolig 300, så boligene skal ha timene først   C: Det spiller ingen rolle: timene blir brukt opp uansett   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Den beste planen avviser alle 30 nybyggforespørslene. Hva sier du til Ronny, og hva vil du vite før du bestemmer deg? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk DB per time (7.2) og differansen mellom planene. Boka nevner selv at bedrifter av og til velger produkter som ikke er lønnsomme isolert, fordi de bidrar til lønnsomhet ellers (7.3, eksempel 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rangeringen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Del DB på timene: ladepunkt 1 050 / 2, solcelleanlegg 4 400 / 14, bolig 900 / 3, nybygg 2 100 / 9. Ta alle ladepunkt og solcelleanlegg først. Hvor mange timer er igjen av 1 080?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronnys rekkefølge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronny sorterer etter DB per jobb: solcelle, nybygg, ladepunkt, bolig. Nybygg gir 233 kr per time, bolig 300. Hver time nybygget tar fra boligene, koster 67 kr.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 7, avsnitt 7.1–7.2 med tabell 7.3, og oppgave 4 i kapitlet. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -188,18 +218,42 @@
     <t xml:space="preserve">a)  Dekningsbidraget for én elbillader, i kroner: pris (timer × 890 + materiell med 20 % påslag) minus variable kostnader (materiell til innkjøpspris + timer × 590).</t>
   </si>
   <si>
+    <t xml:space="preserve">Dekningsbidrag per enhet = salgspris − variable kostnader per enhet (Økonomistyring 7.2, tabell 7.1; kap. 5.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Dekningsbidraget per montørtime for elbilladeren, rundet til hele kroner.</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet av den knappe faktoren = DB per enhet / timer per enhet (Økonomistyring 7.2, tabell 7.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Sett opp planen for mai: fyll de 250 timene ovenfra og ned i rangeringen, aldri flere enn forespurt. Hva blir samlet dekningsbidrag?</t>
   </si>
   <si>
+    <t xml:space="preserve">Fyll kapasiteten i rangert rekkefølge, aldri flere enn forespurt (Økonomistyring 7.2 og oppgave 4 c–e i kapitlet).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona vil ta næringsoppdragene først, fordi de gir 6 400 kr per jobb. Hva skjer med dekningsbidraget i mai?   A: Det øker, fordi næringsoppdragene gir mest per jobb   B: Det er det samme, fordi alle 250 timene blir brukt   C: Det faller med 32 000 kr, fordi næringsoppdragene gir minst per time og fortrenger alle laderne   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Næringskunden er ny og kan gi mer arbeid senere. Hva koster det å ta ett næringsoppdrag i mai likevel, og bør Mona gjøre det? Tips: hvilket oppdrag i planen gir fra seg de 20 timene?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kostnaden ved et avvik = dekningsbidraget fra det som må vike − dekningsbidraget fra det som kommer inn (Økonomistyring 7.2; samme logikk som d).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB for laderen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pris: 3 × 890 + 8 000 × 1,20. Variable kostnader: 8 000 + 3 × 590. Dekningsbidrag = pris − variable kostnader.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planen i mai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rangering per time: lader 833, sikringsskap 500, service 350, næring 320. Ladere og sikringsskap tar 210 av 250 timer. Hvor mange serviceoppdrag à 2 timer får plass i resten?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 7, avsnitt 7.1–7.2 og oppgave 4. Dekningsbidrag i bidragskalkylen: kap. 5.2. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -245,15 +299,36 @@
     <t xml:space="preserve">b)  Ranger etter dekningsbidrag per materiellkrone og fyll materiellrammen ovenfra og ned. Hvor mange solcelleanlegg får plass?</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per krone materialkostnad = DB per enhet / materialkostnad per enhet (Økonomistyring 7.3, eksempel 3, situasjon 2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Samlet dekningsbidrag i juniplanen, i kroner.</t>
   </si>
   <si>
+    <t xml:space="preserve">Samlet dekningsbidrag = summen av antall × DB per enhet (Økonomistyring 7.2–7.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Tom holder fast ved rangeringen etter dekningsbidrag per montørtime, men materiellrammen er den samme. Hva skjer?   A: Det blir det samme, en rangering er en rangering   B: Dekningsbidraget faller med 41 600 kr, fordi nevneren nå skal være materiellkroner   C: Dekningsbidraget øker, fordi montørtimene blir bedre brukt   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Planen bruker 696 av 1 200 montørtimer. 504 timer står ubrukt. Hva bør Kari gjøre? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Verdien av mer av den knappe faktoren er DB per enhet av faktoren for neste oppdrag i køen (følger av 7.2–7.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva er knapt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regn hva forespørslene krever av timer (100 × 2 + 30 × 14 + …) og av materiell (100 × 6 500 + 30 × 38 000 + …). Sammenlikn med 1 200 timer og 1 600 000 kr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ny nevner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB per materiellkrone: bolig 0,23, ladepunkt 0,16, solcelle 0,12, nybygg 0,10. Bolig og ladepunkt tar 1 050 000. Hvor mange solcelleanlegg à 38 000 får plass i resten?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 7, avsnitt 7.3 (eksempel 2 og situasjon 2: knapp råvare målt i kroner). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -287,10 +362,28 @@
     <t xml:space="preserve">b)  Fyll de 60 000 kronene ovenfra og ned i rangeringen etter dekningsbidrag per materiellkrone. Hvor mange sikringsskapbytter får plass?</t>
   </si>
   <si>
+    <t xml:space="preserve">Fyll den knappe faktoren i rangert rekkefølge, aldri flere enn forespurt (Økonomistyring 7.3 og oppgave 4 c–e i kapitlet).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona bruker rangeringen fra mai og tar laderne først. Hva skjer med dekningsbidraget i juni?   A: Det blir best, fordi laderen gir mest per time   B: Det faller til 23 100 kr, fordi laderen binder mest materiell per krone dekningsbidrag   C: Det blir det samme, fordi alle 60 000 kronene brukes   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Planen bruker 170 av 290 timer, og 15 ladere og 10 sikringsskap venter. Hva kan Mona gjøre med det som er knapt? To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingen ny formel. Verdien av en ekstra krone i den knappe faktoren er DB per krone for neste oppdrag i køen (følger av 7.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB per materiellkrone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Del DB på materiellet: næring 6 400 / 2 000, service 700 / 500, sikringsskap 3 000 / 6 000, lader 2 500 / 8 000. Laderen var best i mai. Hvor havner den nå?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planen i juni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Næring (6 000) og service (20 000) først. Da er 34 000 igjen. Hvor mange sikringsskap à 6 000 får plass? Sjekk at timene strekker til.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 7, avsnitt 7.3 (situasjon 2: knapp råvare målt i kroner materialkostnad). Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -304,7 +397,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,8 +464,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,13 +503,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -447,7 +580,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -520,11 +653,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -557,8 +710,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -572,7 +725,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -586,7 +739,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -889,7 +1042,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1050,35 +1203,20 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(93))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="B17" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(385700))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
         <v>40</v>
       </c>
@@ -1086,84 +1224,195 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="17" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F19="","",IF(ABS(F19-(93))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+    <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(385700))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>43</v>
+      </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="25" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="17" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1180,7 +1429,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1191,7 +1440,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1201,7 +1450,7 @@
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1212,7 +1461,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1232,12 +1481,12 @@
         <v>26</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="11" t="n">
@@ -1249,7 +1498,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>3000</v>
@@ -1263,7 +1512,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>700</v>
@@ -1277,7 +1526,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>6400</v>
@@ -1291,7 +1540,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="11" t="n">
@@ -1327,7 +1576,7 @@
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1339,120 +1588,216 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(833))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(139000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="17" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="C","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F19="","",IF(ABS(F19-(833))&lt;=1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(139000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>68</v>
+      </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="17" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1469,7 +1814,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1480,7 +1825,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1490,7 +1835,7 @@
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1501,7 +1846,7 @@
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1512,21 +1857,21 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1050</v>
@@ -1540,7 +1885,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>4400</v>
@@ -1554,7 +1899,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>900</v>
@@ -1568,7 +1913,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>2100</v>
@@ -1582,10 +1927,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>1600000</v>
@@ -1620,13 +1965,13 @@
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="18"/>
+      <c r="F16" s="20"/>
       <c r="G16" s="17" t="str">
         <f aca="false">IF(F16="","",IF(UPPER(TRIM(F16))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1634,7 +1979,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1646,106 +1991,188 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(256600))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="17" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(256600))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="17" t="str">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1762,7 +2189,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1773,7 +2200,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1783,7 +2210,7 @@
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1794,7 +2221,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1805,21 +2232,21 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>2500</v>
@@ -1833,7 +2260,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>3000</v>
@@ -1847,7 +2274,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>700</v>
@@ -1861,7 +2288,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>6400</v>
@@ -1875,10 +2302,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>60000</v>
@@ -1913,7 +2340,7 @@
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1925,120 +2352,216 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(5))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(62200))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="17" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F19="","",IF(ABS(F19-(5))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(62200))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="17" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
@@ -101,7 +101,7 @@
     <t xml:space="preserve">Oppdragstype</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per oppdrag</t>
+    <t xml:space="preserve">Dekningsbidrag per oppdrag</t>
   </si>
   <si>
     <t xml:space="preserve">Timer per oppdrag</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">b)  Ranger etter dekningsbidrag per montørtime og fyll timene ovenfra og ned. Hvor mange boliginstallasjoner får plass i planen?</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet av den knappe faktoren = DB per enhet / forbruk av den knappe faktoren per enhet (Økonomistyring 7.2, tabell 7.3). Planen fyller kapasiteten i rangert rekkefølge, begrenset av hvor mye som kan selges (oppgave 4 c–e i kapitlet).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)  Samlet dekningsbidrag i aprilplanen, i kroner: antall av hver type ganger DB per oppdrag, lagt sammen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samlet dekningsbidrag = summen av antall × DB per enhet for hver type (Økonomistyring 7.2; dekningsbidrag fra kap. 5.2).</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet av den knappe faktoren = dekningsbidrag per enhet / forbruk av den knappe faktoren per enhet (Økonomistyring 7.2, tabell 7.3). Planen fyller kapasiteten i rangert rekkefølge, begrenset av hvor mye som kan selges (oppgave 4 c–e i kapitlet).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)  Samlet dekningsbidrag i aprilplanen, i kroner: antall av hver type ganger dekningsbidrag per oppdrag, lagt sammen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samlet dekningsbidrag = summen av antall × dekningsbidrag per enhet for hver type (Økonomistyring 7.2; dekningsbidrag fra kap. 5.2).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Ronny sier: «Nybygg gir 2 100 kroner per jobb, over dobbelt så mye som en boliginstallasjon. Ta nybyggene før boligene.» Hva er riktig svar?   A: Ronny har rett: høyest dekningsbidrag per jobb skal først   B: Ronny tar feil: nybygg gir 233 kr per montørtime og bolig 300, så boligene skal ha timene først   C: Det spiller ingen rolle: timene blir brukt opp uansett   (skriv bokstaven)</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">e)  Den beste planen avviser alle 30 nybyggforespørslene. Hva sier du til Ronny, og hva vil du vite før du bestemmer deg? To–tre setninger.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingen ny formel. Bruk DB per time (7.2) og differansen mellom planene. Boka nevner selv at bedrifter av og til velger produkter som ikke er lønnsomme isolert, fordi de bidrar til lønnsomhet ellers (7.3, eksempel 3).</t>
+    <t xml:space="preserve">Ingen ny formel. Bruk dekningsbidrag per time (7.2) og differansen mellom planene. Boka nevner selv at bedrifter av og til velger produkter som ikke er lønnsomme isolert, fordi de bidrar til lønnsomhet ellers (7.3, eksempel 3).</t>
   </si>
   <si>
     <t xml:space="preserve">Hint, hvis du står fast</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">Rangeringen</t>
   </si>
   <si>
-    <t xml:space="preserve">Del DB på timene: ladepunkt 1 050 / 2, solcelleanlegg 4 400 / 14, bolig 900 / 3, nybygg 2 100 / 9. Ta alle ladepunkt og solcelleanlegg først. Hvor mange timer er igjen av 1 080?</t>
+    <t xml:space="preserve">Del dekningsbidraget på timene: ladepunkt 1 050 / 2, solcelleanlegg 4 400 / 14, bolig 900 / 3, nybygg 2 100 / 9. Ta alle ladepunkt og solcelleanlegg først. Hvor mange timer er igjen av 1 080?</t>
   </si>
   <si>
     <t xml:space="preserve">Ronnys rekkefølge</t>
   </si>
   <si>
-    <t xml:space="preserve">Ronny sorterer etter DB per jobb: solcelle, nybygg, ladepunkt, bolig. Nybygg gir 233 kr per time, bolig 300. Hver time nybygget tar fra boligene, koster 67 kr.</t>
+    <t xml:space="preserve">Ronny sorterer etter dekningsbidrag per jobb: solcelle, nybygg, ladepunkt, bolig. Nybygg gir 233 kr per time, bolig 300. Hver time nybygget tar fra boligene, koster 67 kr.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 7, avsnitt 7.1–7.2 med tabell 7.3, og oppgave 4 i kapitlet. Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">Kort oppsummert: Dekningsbidraget per oppdrag er pris minus variable kostnader. Når timene er knappe, deler du det på timene oppdraget bruker, og rangerer. Planen fyller timene ovenfra og ned i rangeringen. Den jobben som gir mest per oppdrag, kan godt være den som gir minst per time.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Mai har flere helligdager, og Fjell har 250 fakturerbare timer, mot omtrent 290 en vanlig måned. Forespørslene krever 390 timer. Fjell priser timen til 890 kr uten mva, selger materiellet med 20 % påslag og regner 590 kr per montørtime i direkte lønn (som i kalkylene i kapittel 5). En elbillader i enebolig tar 3 timer og bruker materiell som Fjell kjøper for 8 000 kr. De andre oppdragstypene står i tabellen. Mona Fjell vil ta næringsoppdragene først, fordi de gir mest per jobb og kan gi nye kunder. Regn ut dekningsbidraget for laderen, ranger etter dekningsbidrag per time og sett opp planen for mai.</t>
+    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Mai har flere helligdager, og Fjell har 250 fakturerbare timer, mot omtrent 290 en vanlig måned. Forespørslene krever 390 timer. Fjell priser timen til 890 kr uten merverdiavgift, selger materiellet med 20 % påslag og regner 590 kr per montørtime i direkte lønn (som i kalkylene i kapittel 5). En elbillader i enebolig tar 3 timer og bruker materiell som Fjell kjøper for 8 000 kr. De andre oppdragstypene står i tabellen. Mona Fjell vil ta næringsoppdragene først, fordi de gir mest per jobb og kan gi nye kunder. Regn ut dekningsbidraget for laderen, ranger etter dekningsbidrag per time og sett opp planen for mai.</t>
   </si>
   <si>
     <t xml:space="preserve">Forespurt i mai</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">b)  Dekningsbidraget per montørtime for elbilladeren, rundet til hele kroner.</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet av den knappe faktoren = DB per enhet / timer per enhet (Økonomistyring 7.2, tabell 7.3).</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet av den knappe faktoren = dekningsbidrag per enhet / timer per enhet (Økonomistyring 7.2, tabell 7.3).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Sett opp planen for mai: fyll de 250 timene ovenfra og ned i rangeringen, aldri flere enn forespurt. Hva blir samlet dekningsbidrag?</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">Kostnaden ved et avvik = dekningsbidraget fra det som må vike − dekningsbidraget fra det som kommer inn (Økonomistyring 7.2; samme logikk som d).</t>
   </si>
   <si>
-    <t xml:space="preserve">DB for laderen</t>
+    <t xml:space="preserve">Dekningsbidrag for laderen</t>
   </si>
   <si>
     <t xml:space="preserve">Pris: 3 × 890 + 8 000 × 1,20. Variable kostnader: 8 000 + 3 × 590. Dekningsbidrag = pris − variable kostnader.</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">b)  Ranger etter dekningsbidrag per materiellkrone og fyll materiellrammen ovenfra og ned. Hvor mange solcelleanlegg får plass?</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per krone materialkostnad = DB per enhet / materialkostnad per enhet (Økonomistyring 7.3, eksempel 3, situasjon 2).</t>
+    <t xml:space="preserve">Dekningsbidrag per krone materialkostnad = dekningsbidrag per enhet / materialkostnad per enhet (Økonomistyring 7.3, eksempel 3, situasjon 2).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Samlet dekningsbidrag i juniplanen, i kroner.</t>
   </si>
   <si>
-    <t xml:space="preserve">Samlet dekningsbidrag = summen av antall × DB per enhet (Økonomistyring 7.2–7.3).</t>
+    <t xml:space="preserve">Samlet dekningsbidrag = summen av antall × dekningsbidrag per enhet (Økonomistyring 7.2–7.3).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Tom holder fast ved rangeringen etter dekningsbidrag per montørtime, men materiellrammen er den samme. Hva skjer?   A: Det blir det samme, en rangering er en rangering   B: Dekningsbidraget faller med 41 600 kr, fordi nevneren nå skal være materiellkroner   C: Dekningsbidraget øker, fordi montørtimene blir bedre brukt   (skriv bokstaven)</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">e)  Planen bruker 696 av 1 200 montørtimer. 504 timer står ubrukt. Hva bør Kari gjøre? To–tre setninger.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingen ny formel. Verdien av mer av den knappe faktoren er DB per enhet av faktoren for neste oppdrag i køen (følger av 7.2–7.3).</t>
+    <t xml:space="preserve">Ingen ny formel. Verdien av mer av den knappe faktoren er dekningsbidrag per enhet av faktoren for neste oppdrag i køen (følger av 7.2–7.3).</t>
   </si>
   <si>
     <t xml:space="preserve">Hva er knapt?</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Ny nevner</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per materiellkrone: bolig 0,23, ladepunkt 0,16, solcelle 0,12, nybygg 0,10. Bolig og ladepunkt tar 1 050 000. Hvor mange solcelleanlegg à 38 000 får plass i resten?</t>
+    <t xml:space="preserve">Dekningsbidrag per materiellkrone: bolig 0,23, ladepunkt 0,16, solcelle 0,12, nybygg 0,10. Bolig og ladepunkt tar 1 050 000. Hvor mange solcelleanlegg à 38 000 får plass i resten?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 7, avsnitt 7.3 (eksempel 2 og situasjon 2: knapp råvare målt i kroner). Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Kort oppsummert: Når pengene til materiell er det knappe, deler du dekningsbidraget på materiellkronene oppdraget binder. Oppdrag med mye materiell per time, som var best når timene var knappe, kan da havne nederst. Rangeringen avhenger av hvilken faktor det er knapphet på.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Grossisten gir 30 dagers kreditt, men med en kredittgrense, og etter mva-terminen 10. juni er kontoen trang. I juni kan Fjell derfor bare kjøpe materiell for 60 000 kr (innkjøpspris uten mva). Fjell har 290 fakturerbare timer. Oppdragstypene er de samme som i mai (A2). Forespørslene står i tabellen. Mona vil bruke rangeringen fra mai, der laderen var best. Finn riktig rangering og sett opp planen for juni.</t>
+    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Grossisten gir 30 dagers kreditt, men med en kredittgrense, og etter merverdiavgiftsterminen 10. juni er kontoen trang. I juni kan Fjell derfor bare kjøpe materiell for 60 000 kr (innkjøpspris uten merverdiavgift). Fjell har 290 fakturerbare timer. Oppdragstypene er de samme som i mai (A2). Forespørslene står i tabellen. Mona vil bruke rangeringen fra mai, der laderen var best. Finn riktig rangering og sett opp planen for juni.</t>
   </si>
   <si>
     <t xml:space="preserve">Elbillader (3 t)</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">e)  Planen bruker 170 av 290 timer, og 15 ladere og 10 sikringsskap venter. Hva kan Mona gjøre med det som er knapt? To–tre setninger.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingen ny formel. Verdien av en ekstra krone i den knappe faktoren er DB per krone for neste oppdrag i køen (følger av 7.3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB per materiellkrone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Del DB på materiellet: næring 6 400 / 2 000, service 700 / 500, sikringsskap 3 000 / 6 000, lader 2 500 / 8 000. Laderen var best i mai. Hvor havner den nå?</t>
+    <t xml:space="preserve">Ingen ny formel. Verdien av en ekstra krone i den knappe faktoren er dekningsbidrag per krone for neste oppdrag i køen (følger av 7.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekningsbidrag per materiellkrone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Del dekningsbidraget på materiellet: næring 6 400 / 2 000, service 700 / 500, sikringsskap 3 000 / 6 000, lader 2 500 / 8 000. Laderen var best i mai. Hvor havner den nå?</t>
   </si>
   <si>
     <t xml:space="preserve">Planen i juni</t>
@@ -1344,7 +1344,7 @@
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
     </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
         <v>48</v>
       </c>
@@ -1459,7 +1459,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>56</v>
       </c>

--- a/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="121">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 7: Produktvalg med én knapp faktor (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 7: Produktvalg med én knapp faktor (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok07/OK07_Klasseoppgaver_v5.xlsx
@@ -194,7 +194,7 @@
     <t xml:space="preserve">Kort oppsummert: Dekningsbidraget per oppdrag er pris minus variable kostnader. Når timene er knappe, deler du det på timene oppdraget bruker, og rangerer. Planen fyller timene ovenfra og ned i rangeringen. Den jobben som gir mest per oppdrag, kan godt være den som gir minst per time.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Mai har flere helligdager, og Fjell har 250 fakturerbare timer, mot omtrent 290 en vanlig måned. Forespørslene krever 390 timer. Fjell priser timen til 890 kr uten merverdiavgift, selger materiellet med 20 % påslag og regner 590 kr per montørtime i direkte lønn (som i kalkylene i kapittel 5). En elbillader i enebolig tar 3 timer og bruker materiell som Fjell kjøper for 8 000 kr. De andre oppdragstypene står i tabellen. Mona Fjell vil ta næringsoppdragene først, fordi de gir mest per jobb og kan gi nye kunder. Regn ut dekningsbidraget for laderen, ranger etter dekningsbidrag per time og sett opp planen for mai.</t>
+    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Mai har flere helligdager, og Fjell har 250 fakturerbare timer, mot omtrent 290 en vanlig måned (3 500 timer i året / 12). Forespørslene krever 390 timer. Fjell priser timen til 890 kr uten merverdiavgift, selger materiellet med 20 % påslag og regner 590 kr per montørtime i direkte lønn (som i kalkylene i kapittel 5). En elbillader i enebolig tar 3 timer og bruker materiell som Fjell kjøper for 8 000 kr. De andre oppdragstypene står i tabellen. Mona Fjell vil ta næringsoppdragene først, fordi de gir mest per jobb og kan gi nye kunder. Regn ut dekningsbidraget for laderen, ranger etter dekningsbidrag per time og sett opp planen for mai.</t>
   </si>
   <si>
     <t xml:space="preserve">Forespurt i mai</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Kort oppsummert: Når pengene til materiell er det knappe, deler du dekningsbidraget på materiellkronene oppdraget binder. Oppdrag med mye materiell per time, som var best når timene var knappe, kan da havne nederst. Rangeringen avhenger av hvilken faktor det er knapphet på.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Grossisten gir 30 dagers kreditt, men med en kredittgrense, og etter merverdiavgiftsterminen 10. juni er kontoen trang. I juni kan Fjell derfor bare kjøpe materiell for 60 000 kr (innkjøpspris uten merverdiavgift). Fjell har 290 fakturerbare timer. Oppdragstypene er de samme som i mai (A2). Forespørslene står i tabellen. Mona vil bruke rangeringen fra mai, der laderen var best. Finn riktig rangering og sett opp planen for juni.</t>
+    <t xml:space="preserve">Fjell Elektro AS er i sitt første driftsår. Grossisten gir 30 dagers kreditt, men med en kredittgrense, og etter merverdiavgiftsterminen 10. juni er kontoen trang. I juni kan Fjell derfor bare kjøpe materiell for 60 000 kr (innkjøpspris uten merverdiavgift). Fjell har 290 fakturerbare timer, som en vanlig måned (3 500 timer i året / 12). Oppdragstypene er de samme som i mai (A2). Forespørslene står i tabellen. Mona vil bruke rangeringen fra mai, der laderen var best. Finn riktig rangering og sett opp planen for juni.</t>
   </si>
   <si>
     <t xml:space="preserve">Elbillader (3 t)</t>
